--- a/data/google-spreadsheet/M3GIM-Personenindex.xlsx
+++ b/data/google-spreadsheet/M3GIM-Personenindex.xlsx
@@ -11,14 +11,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="927">
   <si>
     <t>m3gim_id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>wikidata_id</t>
   </si>
   <si>
@@ -46,6 +43,9 @@
     <t xml:space="preserve">Kritiker </t>
   </si>
   <si>
+    <t>Aldenhoff, Bernd</t>
+  </si>
+  <si>
     <t>P3</t>
   </si>
   <si>
@@ -58,12 +58,21 @@
     <t>Altmann, Olga</t>
   </si>
   <si>
+    <t>P301</t>
+  </si>
+  <si>
+    <t>Angerer, Dr. Dorothea</t>
+  </si>
+  <si>
     <t>P5</t>
   </si>
   <si>
     <t>Appia, Adolphe</t>
   </si>
   <si>
+    <t>Bühnenbildner</t>
+  </si>
+  <si>
     <t>P6</t>
   </si>
   <si>
@@ -124,6 +133,15 @@
     <t>Barlach, Ernst</t>
   </si>
   <si>
+    <t>P302</t>
+  </si>
+  <si>
+    <t>Barth, Irmgard</t>
+  </si>
+  <si>
+    <t>Mezzosopranistin, vorname recherchiert</t>
+  </si>
+  <si>
     <t>P14</t>
   </si>
   <si>
@@ -196,6 +214,9 @@
     <t>1838-1875</t>
   </si>
   <si>
+    <t>Björling, Sigurd</t>
+  </si>
+  <si>
     <t>P23</t>
   </si>
   <si>
@@ -232,6 +253,15 @@
     <t>Bonaparte, Napoleon</t>
   </si>
   <si>
+    <t>Bondeville, Emanuel</t>
+  </si>
+  <si>
+    <t>Direktor Opéra National</t>
+  </si>
+  <si>
+    <t>Borkh, Inge</t>
+  </si>
+  <si>
     <t>P26</t>
   </si>
   <si>
@@ -244,6 +274,18 @@
     <t>Braun, Hans</t>
   </si>
   <si>
+    <t>Brenner, Eduard</t>
+  </si>
+  <si>
+    <t>Staatssekretär</t>
+  </si>
+  <si>
+    <t>Bruckner, Anton</t>
+  </si>
+  <si>
+    <t>Bugarinanovic, Melanie</t>
+  </si>
+  <si>
     <t>P28</t>
   </si>
   <si>
@@ -304,9 +346,6 @@
     <t>Cortis, Marcello</t>
   </si>
   <si>
-    <t>Bühnenbildner</t>
-  </si>
-  <si>
     <t>P34</t>
   </si>
   <si>
@@ -325,6 +364,24 @@
     <t>Übersetzer</t>
   </si>
   <si>
+    <t>De Sabata, Victor</t>
+  </si>
+  <si>
+    <t>Dirigent, Vorgönger Karajans bei den Bayreuther Festspielen</t>
+  </si>
+  <si>
+    <t>Dehler, Thomas</t>
+  </si>
+  <si>
+    <t>Bundesminister</t>
+  </si>
+  <si>
+    <t>Delacroix, eugène</t>
+  </si>
+  <si>
+    <t>Maler</t>
+  </si>
+  <si>
     <t>P288</t>
   </si>
   <si>
@@ -382,6 +439,12 @@
     <t>Dünnwald, Josef</t>
   </si>
   <si>
+    <t>P298</t>
+  </si>
+  <si>
+    <t>Dvořák, Antonín</t>
+  </si>
+  <si>
     <t>P43</t>
   </si>
   <si>
@@ -391,12 +454,36 @@
     <t>Beleuchtungsassistent, Unsicher: im Original: directeur de l'éclairage</t>
   </si>
   <si>
+    <t>Beleuchter</t>
+  </si>
+  <si>
+    <t>Edelmann, Otto</t>
+  </si>
+  <si>
+    <t>Ehard, Hans</t>
+  </si>
+  <si>
+    <t>Ministerpräsident</t>
+  </si>
+  <si>
+    <t>Eisenmenger, Arthur</t>
+  </si>
+  <si>
+    <t>technische leitung</t>
+  </si>
+  <si>
     <t>P44</t>
   </si>
   <si>
     <t>Elfriede Ott</t>
   </si>
   <si>
+    <t>Elisabeth, Königin</t>
+  </si>
+  <si>
+    <t>Königin von Belgien</t>
+  </si>
+  <si>
     <t>P45</t>
   </si>
   <si>
@@ -424,6 +511,15 @@
     <t>Fahberg, Antonia</t>
   </si>
   <si>
+    <t>Falcon, Bruni</t>
+  </si>
+  <si>
+    <t>sängerin</t>
+  </si>
+  <si>
+    <t>Faulhaber, Werner</t>
+  </si>
+  <si>
     <t>P49</t>
   </si>
   <si>
@@ -436,6 +532,9 @@
     <t>Ferenz, Willy</t>
   </si>
   <si>
+    <t>Ferrein, Giuliano</t>
+  </si>
+  <si>
     <t>P51</t>
   </si>
   <si>
@@ -445,6 +544,9 @@
     <t>Klavier</t>
   </si>
   <si>
+    <t>Flagstadt, Kirsten</t>
+  </si>
+  <si>
     <t>P52</t>
   </si>
   <si>
@@ -457,6 +559,15 @@
     <t>Sänger (Bariton)</t>
   </si>
   <si>
+    <t>Friedland, Brünnhild</t>
+  </si>
+  <si>
+    <t>P307</t>
+  </si>
+  <si>
+    <t>Fues, willi</t>
+  </si>
+  <si>
     <t>P53</t>
   </si>
   <si>
@@ -475,6 +586,9 @@
     <t>Dirigent, Komponist</t>
   </si>
   <si>
+    <t>Georges Alvès</t>
+  </si>
+  <si>
     <t>P55</t>
   </si>
   <si>
@@ -505,6 +619,9 @@
     <t>Gieseking, Walter</t>
   </si>
   <si>
+    <t>Glotz, Michel</t>
+  </si>
+  <si>
     <t>P59</t>
   </si>
   <si>
@@ -574,6 +691,9 @@
     <t>Händel, Georg Friedrich</t>
   </si>
   <si>
+    <t>Handt, Herbert</t>
+  </si>
+  <si>
     <t>P69</t>
   </si>
   <si>
@@ -583,6 +703,15 @@
     <t>choreograph:in</t>
   </si>
   <si>
+    <t>P310</t>
+  </si>
+  <si>
+    <t>Hartmann, Karl Amadeus</t>
+  </si>
+  <si>
+    <t>Leiter der Musica Viva</t>
+  </si>
+  <si>
     <t>P70</t>
   </si>
   <si>
@@ -592,21 +721,30 @@
     <t>P71</t>
   </si>
   <si>
+    <t>Hartmann, Rudolf Otto</t>
+  </si>
+  <si>
+    <t>Opernregie</t>
+  </si>
+  <si>
+    <t>P287</t>
+  </si>
+  <si>
     <t>Hartmann, Rudolf</t>
   </si>
   <si>
-    <t>Opernregie</t>
-  </si>
-  <si>
-    <t>P287</t>
-  </si>
-  <si>
     <t>P72</t>
   </si>
   <si>
     <t>Hasse, Johann Asolph</t>
   </si>
   <si>
+    <t>P294</t>
+  </si>
+  <si>
+    <t>Haydn, Joseph</t>
+  </si>
+  <si>
     <t>P73</t>
   </si>
   <si>
@@ -628,6 +766,15 @@
     <t>Orgel</t>
   </si>
   <si>
+    <t>P309</t>
+  </si>
+  <si>
+    <t>Herminghaus, A. E.</t>
+  </si>
+  <si>
+    <t>Intendant, von Chorgemeinschaft Wuppertal</t>
+  </si>
+  <si>
     <t>P75</t>
   </si>
   <si>
@@ -640,12 +787,21 @@
     <t>Hinsch-Gröhndal, Natalie</t>
   </si>
   <si>
+    <t>Hirsch, Georges</t>
+  </si>
+  <si>
+    <t>Administrateur Général</t>
+  </si>
+  <si>
     <t>P77</t>
   </si>
   <si>
     <t>Hirsch, Robert</t>
   </si>
   <si>
+    <t>Repräsentant der Syndicat d'initiative (belgisch/frz. Toursimusbund)</t>
+  </si>
+  <si>
     <t>P78</t>
   </si>
   <si>
@@ -691,12 +847,24 @@
     <t xml:space="preserve">Honolka, Kurt Dr. </t>
   </si>
   <si>
+    <t>Hopf, Hans</t>
+  </si>
+  <si>
     <t>P83</t>
   </si>
   <si>
     <t>Horwitz</t>
   </si>
   <si>
+    <t>P303</t>
+  </si>
+  <si>
+    <t>Hotter, Hans</t>
+  </si>
+  <si>
+    <t>sänger</t>
+  </si>
+  <si>
     <t>P84</t>
   </si>
   <si>
@@ -712,6 +880,12 @@
     <t>Violine</t>
   </si>
   <si>
+    <t>Hundhammer, Alois</t>
+  </si>
+  <si>
+    <t>Landtagspräsident</t>
+  </si>
+  <si>
     <t>P86</t>
   </si>
   <si>
@@ -745,6 +919,12 @@
     <t>Sängerin; Vorname fehlt UAKUG/NIM_004, Folio 10 --- Maria von (?)</t>
   </si>
   <si>
+    <t xml:space="preserve">Ilosvay, Maria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sängerin </t>
+  </si>
+  <si>
     <t>P90</t>
   </si>
   <si>
@@ -781,6 +961,9 @@
     <t>Jürgens, Helmut</t>
   </si>
   <si>
+    <t>Karajan, Herbert von</t>
+  </si>
+  <si>
     <t>P95</t>
   </si>
   <si>
@@ -835,12 +1018,27 @@
     <t>1857-1941</t>
   </si>
   <si>
+    <t>Kietz, Ernst Benedikt</t>
+  </si>
+  <si>
+    <t>Maler, Lithograph</t>
+  </si>
+  <si>
     <t>P103</t>
   </si>
   <si>
     <t>Klarwein, Franz</t>
   </si>
   <si>
+    <t>P292</t>
+  </si>
+  <si>
+    <t>Klebe, Karl-Heinz</t>
+  </si>
+  <si>
+    <t>Bayreuther Festspiele</t>
+  </si>
+  <si>
     <t>P104</t>
   </si>
   <si>
@@ -862,6 +1060,27 @@
     <t>Klobučar, Berislav</t>
   </si>
   <si>
+    <t>Klomp, M. Z.</t>
+  </si>
+  <si>
+    <t>Kostümbildner</t>
+  </si>
+  <si>
+    <t>P305</t>
+  </si>
+  <si>
+    <t>Klose</t>
+  </si>
+  <si>
+    <t>Nur als Frau Klose (UAKUG/NIM_011 Folio 18)Evtl. Margarete Klose?</t>
+  </si>
+  <si>
+    <t>Klose, Willi</t>
+  </si>
+  <si>
+    <t>Maskenbidner</t>
+  </si>
+  <si>
     <t>Kmett, Waldemar</t>
   </si>
   <si>
@@ -889,9 +1108,6 @@
     <t>Königin Elisabeth</t>
   </si>
   <si>
-    <t>P294</t>
-  </si>
-  <si>
     <t>Köth, Erika</t>
   </si>
   <si>
@@ -913,18 +1129,33 @@
     <t>Krauß, Clemens</t>
   </si>
   <si>
+    <t>Krayenbühl, Hugo</t>
+  </si>
+  <si>
+    <t>Zürcher Neurochirurg</t>
+  </si>
+  <si>
     <t>P112</t>
   </si>
   <si>
     <t>Kreppel, Walter</t>
   </si>
   <si>
+    <t>Krott, Josef</t>
+  </si>
+  <si>
     <t>P113</t>
   </si>
   <si>
     <t>Kuborn - de Gauquier, Mme</t>
   </si>
   <si>
+    <t>Kuborn de Gauqier</t>
+  </si>
+  <si>
+    <t>Name unvollständig</t>
+  </si>
+  <si>
     <t>P114</t>
   </si>
   <si>
@@ -934,9 +1165,6 @@
     <t>Kuen, Paul</t>
   </si>
   <si>
-    <t>P115</t>
-  </si>
-  <si>
     <t>Kuën, Paul</t>
   </si>
   <si>
@@ -1006,6 +1234,9 @@
     <t>Leimer, Karl</t>
   </si>
   <si>
+    <t>Leitner, Ferdinand</t>
+  </si>
+  <si>
     <t>P125</t>
   </si>
   <si>
@@ -1027,6 +1258,12 @@
     <t>Linné, Carl von</t>
   </si>
   <si>
+    <t>List, Rudolf</t>
+  </si>
+  <si>
+    <t>Journalist (Sontagsblatt für Steiermark)</t>
+  </si>
+  <si>
     <t>P128</t>
   </si>
   <si>
@@ -1057,6 +1294,9 @@
     <t>Lohmann, Paul</t>
   </si>
   <si>
+    <t>London, George</t>
+  </si>
+  <si>
     <t>P132</t>
   </si>
   <si>
@@ -1069,18 +1309,30 @@
     <t>Lorenz, Gerlinde</t>
   </si>
   <si>
+    <t>Lorenz, Max</t>
+  </si>
+  <si>
     <t>P134</t>
   </si>
   <si>
     <t>Lortzing, Albert</t>
   </si>
   <si>
+    <t>Lubin, Germaine</t>
+  </si>
+  <si>
+    <t>Ludwig, Hanna</t>
+  </si>
+  <si>
     <t>P135</t>
   </si>
   <si>
     <t>Lustigs, Rudolf</t>
   </si>
   <si>
+    <t>Maghini, Ruggero</t>
+  </si>
+  <si>
     <t>P136</t>
   </si>
   <si>
@@ -1129,6 +1381,12 @@
     <t>Vater</t>
   </si>
   <si>
+    <t>Mallarme, Stéphane</t>
+  </si>
+  <si>
+    <t>französischer Schriftsteller</t>
+  </si>
+  <si>
     <t>P141</t>
   </si>
   <si>
@@ -1183,12 +1441,21 @@
     <t>UAKUG/NIM_007_10 Regierungsrat (Intendanz Bayerische Staatsoper)</t>
   </si>
   <si>
+    <t>Mendelssohn Bartholdy, Felix</t>
+  </si>
+  <si>
     <t>P149</t>
   </si>
   <si>
     <t>Menotti, Gian Carlo</t>
   </si>
   <si>
+    <t>Messerschmitt, Willy</t>
+  </si>
+  <si>
+    <t>FLugzeugkonstrukteur</t>
+  </si>
+  <si>
     <t>P150</t>
   </si>
   <si>
@@ -1228,6 +1495,9 @@
     <t>Mitropoulos, Dimitri</t>
   </si>
   <si>
+    <t>Mittag, Erwin</t>
+  </si>
+  <si>
     <t>P156</t>
   </si>
   <si>
@@ -1240,9 +1510,6 @@
     <t>Moralt, Rudolf</t>
   </si>
   <si>
-    <t>P292</t>
-  </si>
-  <si>
     <t>P158</t>
   </si>
   <si>
@@ -1255,6 +1522,9 @@
     <t>Mozart, Wolfgang Amadeus</t>
   </si>
   <si>
+    <t>Müller-Minervo, Otto</t>
+  </si>
+  <si>
     <t>P160</t>
   </si>
   <si>
@@ -1276,9 +1546,6 @@
     <t>Neidlinger, Gustav</t>
   </si>
   <si>
-    <t>P163</t>
-  </si>
-  <si>
     <t>P164</t>
   </si>
   <si>
@@ -1324,6 +1591,9 @@
     <t>Orff, Carl</t>
   </si>
   <si>
+    <t>Komponist, Musikpädagoge</t>
+  </si>
+  <si>
     <t>P171</t>
   </si>
   <si>
@@ -1351,12 +1621,27 @@
     <t>Arrangeur</t>
   </si>
   <si>
+    <t>Pergolesi, Giovanni Battista</t>
+  </si>
+  <si>
     <t>P175</t>
   </si>
   <si>
     <t>Peter, Albrecht</t>
   </si>
   <si>
+    <t>Pfeiffer, Anton</t>
+  </si>
+  <si>
+    <t>deutscher Botschafter in Belgien</t>
+  </si>
+  <si>
+    <t>Pfeiffer, Elsa</t>
+  </si>
+  <si>
+    <t>Frau von deutschem Botschafter Belgien</t>
+  </si>
+  <si>
     <t>P176</t>
   </si>
   <si>
@@ -1375,6 +1660,9 @@
     <t>Pfitzner, Hans</t>
   </si>
   <si>
+    <t>Pflanzl, Heinrich</t>
+  </si>
+  <si>
     <t>P179</t>
   </si>
   <si>
@@ -1393,6 +1681,9 @@
     <t>Chroleiter</t>
   </si>
   <si>
+    <t>chorleiter</t>
+  </si>
+  <si>
     <t>P181</t>
   </si>
   <si>
@@ -1447,6 +1738,18 @@
     <t>Chordirigieren/Orgel</t>
   </si>
   <si>
+    <t>Rappl, Erich</t>
+  </si>
+  <si>
+    <t>Journalist, Musikwissenschaftler</t>
+  </si>
+  <si>
+    <t>Reding, Janine</t>
+  </si>
+  <si>
+    <t>Pianistin</t>
+  </si>
+  <si>
     <t>P188</t>
   </si>
   <si>
@@ -1468,6 +1771,9 @@
     <t>Ausstatter</t>
   </si>
   <si>
+    <t>Reissinger, Hans C.</t>
+  </si>
+  <si>
     <t>P191</t>
   </si>
   <si>
@@ -1477,6 +1783,9 @@
     <t>Sängerin; Vorname fehlt UAKUG/NIM_004, Folio 10 --- Regina (?)</t>
   </si>
   <si>
+    <t>Resnik, Regina</t>
+  </si>
+  <si>
     <t>P192</t>
   </si>
   <si>
@@ -1495,6 +1804,9 @@
     <t>Rodzinski, Artur</t>
   </si>
   <si>
+    <t>Rogatchewsky, Joseph</t>
+  </si>
+  <si>
     <t>P195</t>
   </si>
   <si>
@@ -1507,12 +1819,24 @@
     <t>Rogatschewsky, Mme</t>
   </si>
   <si>
+    <t>Rohr, Otto von</t>
+  </si>
+  <si>
     <t>P197</t>
   </si>
   <si>
     <t>Roller, Alfred</t>
   </si>
   <si>
+    <t>P306</t>
+  </si>
+  <si>
+    <t>Rollwagen, Hans</t>
+  </si>
+  <si>
+    <t>Oberbürgermeister Stadt Bayreuth</t>
+  </si>
+  <si>
     <t>P198</t>
   </si>
   <si>
@@ -1534,6 +1858,12 @@
     <t>chorleiter:in</t>
   </si>
   <si>
+    <t>Röthlisberger, Max</t>
+  </si>
+  <si>
+    <t>Ausstattungsdirektor (Oper Zürich)</t>
+  </si>
+  <si>
     <t>P201</t>
   </si>
   <si>
@@ -1567,6 +1897,15 @@
     <t>Samazeuilh, Gustave</t>
   </si>
   <si>
+    <t>P269</t>
+  </si>
+  <si>
+    <t>Sattler, Dieter</t>
+  </si>
+  <si>
+    <t>Präsident des Bayrischen Rundfunkrats</t>
+  </si>
+  <si>
     <t>P206</t>
   </si>
   <si>
@@ -1582,6 +1921,9 @@
     <t xml:space="preserve">Jounalist </t>
   </si>
   <si>
+    <t>Schäffer, Fritz</t>
+  </si>
+  <si>
     <t>P208</t>
   </si>
   <si>
@@ -1609,6 +1951,9 @@
     <t>Schellenberg, Arno</t>
   </si>
   <si>
+    <t>Schlüter, Erna</t>
+  </si>
+  <si>
     <t>P212</t>
   </si>
   <si>
@@ -1621,6 +1966,9 @@
     <t>Schmidt, Franz</t>
   </si>
   <si>
+    <t>Schneider, Hugo</t>
+  </si>
+  <si>
     <t>P214</t>
   </si>
   <si>
@@ -1630,15 +1978,30 @@
     <t xml:space="preserve">identifikation felht </t>
   </si>
   <si>
+    <t>P299</t>
+  </si>
+  <si>
+    <t>Schoeck</t>
+  </si>
+  <si>
+    <t>verm. Schoeck, Othmar, Komponist</t>
+  </si>
+  <si>
     <t>P215</t>
   </si>
   <si>
     <t>Schöffler, Paul</t>
   </si>
   <si>
+    <t>Schubert, Erika</t>
+  </si>
+  <si>
     <t>Schubert, Franz</t>
   </si>
   <si>
+    <t>Schubert, Willi</t>
+  </si>
+  <si>
     <t>P216</t>
   </si>
   <si>
@@ -1687,6 +2050,27 @@
     <t>(Kinder-)Chorleiter</t>
   </si>
   <si>
+    <t>Schwarzkopf, Elisabeth</t>
+  </si>
+  <si>
+    <t>Schwennicke, Fritz</t>
+  </si>
+  <si>
+    <t>Fotograf</t>
+  </si>
+  <si>
+    <t>Seebohm, Hans-Christopher</t>
+  </si>
+  <si>
+    <t>Politiker, Bundesminister</t>
+  </si>
+  <si>
+    <t>Seidel, Hanns</t>
+  </si>
+  <si>
+    <t>Wirtschaftminister Bayern</t>
+  </si>
+  <si>
     <t>P222</t>
   </si>
   <si>
@@ -1708,6 +2092,9 @@
     <t>Instrumentalist, Englisch-Horn (Vorname unklar)</t>
   </si>
   <si>
+    <t>Siewert, Ruth</t>
+  </si>
+  <si>
     <t>P225</t>
   </si>
   <si>
@@ -1717,6 +2104,12 @@
     <t>Technischer Leiter</t>
   </si>
   <si>
+    <t>Singer, Joseph</t>
+  </si>
+  <si>
+    <t>Präsident des Bayrischen Senats</t>
+  </si>
+  <si>
     <t>P226</t>
   </si>
   <si>
@@ -1735,6 +2128,12 @@
     <t>Sophokles</t>
   </si>
   <si>
+    <t>Sorrell, Ilse</t>
+  </si>
+  <si>
+    <t>Steber, Eleanor</t>
+  </si>
+  <si>
     <t>P229</t>
   </si>
   <si>
@@ -1756,6 +2155,12 @@
     <t>Stolze, Gerhard</t>
   </si>
   <si>
+    <t xml:space="preserve">Stolze, Gerhard </t>
+  </si>
+  <si>
+    <t>Strachwitz von Gross-Zauche und Camminetz, Hyacinth</t>
+  </si>
+  <si>
     <t>P232</t>
   </si>
   <si>
@@ -1777,12 +2182,27 @@
     <t>1882-1971</t>
   </si>
   <si>
+    <t>Streich, Rita</t>
+  </si>
+  <si>
+    <t>Strelow, Liselotte</t>
+  </si>
+  <si>
+    <t>Fotografin</t>
+  </si>
+  <si>
     <t>P235</t>
   </si>
   <si>
     <t>Süßmayr, Franz Xaver</t>
   </si>
   <si>
+    <t>P297</t>
+  </si>
+  <si>
+    <t>Suter, Hermann</t>
+  </si>
+  <si>
     <t>P236</t>
   </si>
   <si>
@@ -1801,7 +2221,7 @@
     <t>P238</t>
   </si>
   <si>
-    <t>Szemere</t>
+    <t>Szemere, László</t>
   </si>
   <si>
     <t>P239</t>
@@ -1825,13 +2245,19 @@
     <t>Agent Wien</t>
   </si>
   <si>
+    <t>P304</t>
+  </si>
+  <si>
+    <t>Thebom, Blanche</t>
+  </si>
+  <si>
     <t>P242</t>
   </si>
   <si>
     <t>Thiel, Fred</t>
   </si>
   <si>
-    <t>Kostümbildner</t>
+    <t>Thomamüller, Liselotte</t>
   </si>
   <si>
     <t>P243</t>
@@ -1852,6 +2278,12 @@
     <t>Tobin, Gene</t>
   </si>
   <si>
+    <t>Töpper, Hertha</t>
+  </si>
+  <si>
+    <t>Toscanini, Arturo</t>
+  </si>
+  <si>
     <t>P246</t>
   </si>
   <si>
@@ -1870,12 +2302,18 @@
     <t>Traxel, Josef</t>
   </si>
   <si>
+    <t>Treptow, Günther</t>
+  </si>
+  <si>
     <t>P249</t>
   </si>
   <si>
     <t>Uhde, Hermann</t>
   </si>
   <si>
+    <t>Unger, Gerhard</t>
+  </si>
+  <si>
     <t>P250</t>
   </si>
   <si>
@@ -1900,6 +2338,12 @@
     <t>Vacchiano</t>
   </si>
   <si>
+    <t>Valabrega, Cesare</t>
+  </si>
+  <si>
+    <t>Musikwissenschaftler</t>
+  </si>
+  <si>
     <t>P253</t>
   </si>
   <si>
@@ -1945,6 +2389,15 @@
     <t>voioumaa, Mme</t>
   </si>
   <si>
+    <t>Voioumaa, Väinö</t>
+  </si>
+  <si>
+    <t>finnischer Minister</t>
+  </si>
+  <si>
+    <t>von Ilosvay, Maria</t>
+  </si>
+  <si>
     <t>P260</t>
   </si>
   <si>
@@ -1957,6 +2410,18 @@
     <t>Wächter, Eberhard</t>
   </si>
   <si>
+    <t>Wagner, Ellen</t>
+  </si>
+  <si>
+    <t>Frau von Wolfgang Wagner, nach Scheidung: Drexel, Ellen</t>
+  </si>
+  <si>
+    <t>Wagner, Gertrud</t>
+  </si>
+  <si>
+    <t>Frau von Wieland Wagner, regisseurassistenz</t>
+  </si>
+  <si>
     <t>P262</t>
   </si>
   <si>
@@ -1978,6 +2443,15 @@
     <t>Wagner, Wieland</t>
   </si>
   <si>
+    <t>Leiter der Bayreuthen Festspiele</t>
+  </si>
+  <si>
+    <t>regisseur</t>
+  </si>
+  <si>
+    <t>Wagner, Wieland Gottfried</t>
+  </si>
+  <si>
     <t>P265</t>
   </si>
   <si>
@@ -1987,7 +2461,7 @@
     <t>Q60452</t>
   </si>
   <si>
-    <t>Festspielleiter Bayreuth, Regisseur</t>
+    <t>Festspielleiter Bayreuth, Regisseur, Leiter der Bayreuthe Festspiele</t>
   </si>
   <si>
     <t>P266</t>
@@ -2014,226 +2488,310 @@
     <t xml:space="preserve">Agent? </t>
   </si>
   <si>
-    <t>P269</t>
+    <t>P300</t>
+  </si>
+  <si>
+    <t>Weber</t>
+  </si>
+  <si>
+    <t>P270</t>
+  </si>
+  <si>
+    <t>Wehofschitz, Kurt</t>
+  </si>
+  <si>
+    <t>P271</t>
+  </si>
+  <si>
+    <t>Wehrli., Dr.</t>
+  </si>
+  <si>
+    <t>P272</t>
+  </si>
+  <si>
+    <t>Weishappel, Rudolf</t>
+  </si>
+  <si>
+    <t>P273</t>
+  </si>
+  <si>
+    <t>Welt, Alfred</t>
+  </si>
+  <si>
+    <t>P274</t>
+  </si>
+  <si>
+    <t>Werba, Erik</t>
+  </si>
+  <si>
+    <t>Pianist</t>
+  </si>
+  <si>
+    <t>P275</t>
+  </si>
+  <si>
+    <t>Wesendonck, Mathilde</t>
+  </si>
+  <si>
+    <t>P276</t>
+  </si>
+  <si>
+    <t>Wiener, Otto</t>
+  </si>
+  <si>
+    <t>P277</t>
+  </si>
+  <si>
+    <t>Wieter, Georg</t>
+  </si>
+  <si>
+    <t>Wilhelm, Rolf Alexander</t>
+  </si>
+  <si>
+    <t>abgeleitet aus Unterschrift; Nordwestdeutschen Rundfunks; Komponist</t>
+  </si>
+  <si>
+    <t>P278</t>
+  </si>
+  <si>
+    <t>Willy Heyer</t>
+  </si>
+  <si>
+    <t>P279</t>
+  </si>
+  <si>
+    <t>Windgassen, Wolfgang</t>
+  </si>
+  <si>
+    <t>P280</t>
+  </si>
+  <si>
+    <t>Wißmann, Lore</t>
+  </si>
+  <si>
+    <t>P281</t>
+  </si>
+  <si>
+    <t>Wissner, Otto</t>
+  </si>
+  <si>
+    <t>Wißner, Otto</t>
+  </si>
+  <si>
+    <t>ausstattungsleitung</t>
+  </si>
+  <si>
+    <t>Witte, Erich</t>
+  </si>
+  <si>
+    <t>P282</t>
+  </si>
+  <si>
+    <t>Witte, Wolfgang</t>
+  </si>
+  <si>
+    <t>P283</t>
+  </si>
+  <si>
+    <t>Wolf, Hugo</t>
+  </si>
+  <si>
+    <t>P284</t>
+  </si>
+  <si>
+    <t>Wolf, Winfried</t>
+  </si>
+  <si>
+    <t>P308</t>
+  </si>
+  <si>
+    <t>Wylach, G.</t>
+  </si>
+  <si>
+    <t>Konzertdirektion</t>
+  </si>
+  <si>
+    <t>P285</t>
+  </si>
+  <si>
+    <t>Y.</t>
+  </si>
+  <si>
+    <t>Kritiker (unvollständig: UAKUG/NIM_004, Folio 16)</t>
+  </si>
+  <si>
+    <t>Zadek, Hilde</t>
+  </si>
+  <si>
+    <t>Zimmermann, Erika</t>
+  </si>
+  <si>
+    <t>Deinert, Herbert</t>
+  </si>
+  <si>
+    <t>Jorissen, Ingrid</t>
+  </si>
+  <si>
+    <t>Kostümbildnerin</t>
+  </si>
+  <si>
+    <t>Eisenschmidt, Arthur</t>
+  </si>
+  <si>
+    <t>Dalberg, Friedrich</t>
+  </si>
+  <si>
+    <t>Sänger:in</t>
+  </si>
+  <si>
+    <t>Berg, Hans</t>
+  </si>
+  <si>
+    <t>Janko, Josef</t>
+  </si>
+  <si>
+    <t>Mikorey, Karl</t>
+  </si>
+  <si>
+    <t>Tandler, Heinz</t>
+  </si>
+  <si>
+    <t>Borst, Heinz</t>
+  </si>
+  <si>
+    <t>Mill, Arnold van</t>
+  </si>
+  <si>
+    <t>Hager, Paul</t>
+  </si>
+  <si>
+    <t>Regieassistent</t>
+  </si>
+  <si>
+    <t>Kaulbach, Margarete</t>
+  </si>
+  <si>
+    <t>Kostümbilderin</t>
+  </si>
+  <si>
+    <t>Lausch, Eleanor</t>
+  </si>
+  <si>
+    <t>Wild Elfriede</t>
+  </si>
+  <si>
+    <t>Gruder-Guntram, Hugo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorname unsicher </t>
+  </si>
+  <si>
+    <t>Piel, Emma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brüssel Ansprechpartnerin Für Gastspiel der Bayreuther Festspiele </t>
+  </si>
+  <si>
+    <t>Nillson, Birgit</t>
   </si>
   <si>
     <t>Weber, Ludwig</t>
   </si>
   <si>
-    <t>P270</t>
-  </si>
-  <si>
-    <t>Wehofschitz, Kurt</t>
-  </si>
-  <si>
-    <t>P271</t>
-  </si>
-  <si>
-    <t>Wehrli., Dr.</t>
-  </si>
-  <si>
-    <t>P272</t>
-  </si>
-  <si>
-    <t>Weishappel, Rudolf</t>
-  </si>
-  <si>
-    <t>P273</t>
-  </si>
-  <si>
-    <t>Welt, Alfred</t>
-  </si>
-  <si>
-    <t>P274</t>
-  </si>
-  <si>
-    <t>Werba, Erik</t>
-  </si>
-  <si>
-    <t>Pianist</t>
-  </si>
-  <si>
-    <t>P275</t>
-  </si>
-  <si>
-    <t>Wesendonck, Mathilde</t>
-  </si>
-  <si>
-    <t>P276</t>
-  </si>
-  <si>
-    <t>Wiener, Otto</t>
-  </si>
-  <si>
-    <t>P277</t>
-  </si>
-  <si>
-    <t>Wieter, Georg</t>
-  </si>
-  <si>
-    <t>P278</t>
-  </si>
-  <si>
-    <t>Willy Heyer</t>
-  </si>
-  <si>
-    <t>P279</t>
-  </si>
-  <si>
-    <t>Windgassen, Wolfgang</t>
-  </si>
-  <si>
-    <t>P280</t>
-  </si>
-  <si>
-    <t>Wißmann, Lore</t>
-  </si>
-  <si>
-    <t>P281</t>
-  </si>
-  <si>
-    <t>Wissner, Otto</t>
-  </si>
-  <si>
-    <t>P282</t>
-  </si>
-  <si>
-    <t>Witte, Wolfgang</t>
-  </si>
-  <si>
-    <t>P283</t>
-  </si>
-  <si>
-    <t>Wolf, Hugo</t>
-  </si>
-  <si>
-    <t>P284</t>
-  </si>
-  <si>
-    <t>Wolf, Winfried</t>
-  </si>
-  <si>
-    <t>P285</t>
-  </si>
-  <si>
-    <t>Y.</t>
-  </si>
-  <si>
-    <t>Kritiker (unvollständig: UAKUG/NIM_004, Folio 16)</t>
-  </si>
-  <si>
-    <t>Zadek, Hilde</t>
-  </si>
-  <si>
-    <t>Zimmermann, Erika</t>
-  </si>
-  <si>
-    <t>Zimmermann, Wolfram</t>
-  </si>
-  <si>
-    <t>Röthlisberger, Max</t>
-  </si>
-  <si>
-    <t>Ausstattungsdirektor (Oper Zürich)</t>
-  </si>
-  <si>
-    <t>List, Rudolf</t>
-  </si>
-  <si>
-    <t>Journalist (Sontagsblatt für Steiermark)</t>
-  </si>
-  <si>
-    <t>Krayenbühl, Hugo</t>
-  </si>
-  <si>
-    <t>Zürcher Neurochirurg</t>
-  </si>
-  <si>
-    <t>Klebe, Karl-Heinz</t>
-  </si>
-  <si>
-    <t>Bayreuther Festspiele</t>
-  </si>
-  <si>
-    <t>Bruckner, Anton</t>
-  </si>
-  <si>
-    <t>Haydn, Joseph</t>
-  </si>
-  <si>
-    <t>Mendelssohn Bartholdy, Felix</t>
-  </si>
-  <si>
-    <t>Pergolesi, Giovanni Battista</t>
-  </si>
-  <si>
-    <t>P297</t>
-  </si>
-  <si>
-    <t>Suter, Hermann</t>
-  </si>
-  <si>
-    <t>P298</t>
-  </si>
-  <si>
-    <t>Dvořák, Antonín</t>
-  </si>
-  <si>
-    <t>P299</t>
-  </si>
-  <si>
-    <t>Schoeck</t>
-  </si>
-  <si>
-    <t>verm. Schoeck, Othmar, Komponist</t>
-  </si>
-  <si>
-    <t>P300</t>
-  </si>
-  <si>
-    <t>Weber</t>
-  </si>
-  <si>
-    <t>P301</t>
-  </si>
-  <si>
-    <t>Angerer, Dr. Dorothea</t>
-  </si>
-  <si>
-    <t>P302</t>
-  </si>
-  <si>
-    <t>Barth, Irmgard</t>
-  </si>
-  <si>
-    <t>Mezzosopranistin, vorname recherchiert</t>
-  </si>
-  <si>
-    <t>P303</t>
-  </si>
-  <si>
-    <t>Hotter, Hans</t>
-  </si>
-  <si>
-    <t>P304</t>
-  </si>
-  <si>
-    <t>P305</t>
-  </si>
-  <si>
-    <t>P306</t>
-  </si>
-  <si>
-    <t>P307</t>
-  </si>
-  <si>
-    <t>P308</t>
-  </si>
-  <si>
-    <t>P309</t>
-  </si>
-  <si>
-    <t>P310</t>
+    <t>Jaumonet, Leopold</t>
+  </si>
+  <si>
+    <t>Journalist, Radio Monte Carlo</t>
+  </si>
+  <si>
+    <t>Wirz, Karl Andreas</t>
+  </si>
+  <si>
+    <t>Bayrischer Rundfunk</t>
+  </si>
+  <si>
+    <t>Schröter, Andreas</t>
+  </si>
+  <si>
+    <t>Moltkau, Hans</t>
+  </si>
+  <si>
+    <t>Komponist, Dirigent, Bayrischer Rundfunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koch, Karl O. </t>
+  </si>
+  <si>
+    <t>Regisseur, Rundfunkredakteur, Westdeutscher Rundfunk</t>
+  </si>
+  <si>
+    <t>Marszalek, Franz</t>
+  </si>
+  <si>
+    <t>Wienke, Gerhard</t>
+  </si>
+  <si>
+    <t>Süddeutscher Rundfunk, Musikwissenschaftler</t>
+  </si>
+  <si>
+    <t>Matzerath, Otto</t>
+  </si>
+  <si>
+    <t>Dirigent, Hessischer Rundfunk</t>
+  </si>
+  <si>
+    <t>Müller-Kray, Hans</t>
+  </si>
+  <si>
+    <t>Dirigent, Süddeutscher Rundfunk</t>
+  </si>
+  <si>
+    <t>Hopf, Gertraud</t>
+  </si>
+  <si>
+    <t>Strauss, Richard Junior</t>
+  </si>
+  <si>
+    <t>Fekesa, Jörg</t>
+  </si>
+  <si>
+    <t>Czerwenka, Oskar</t>
+  </si>
+  <si>
+    <t>Diehl, André</t>
+  </si>
+  <si>
+    <t>Pernerstorfer, Alois</t>
+  </si>
+  <si>
+    <t>Zallinger, Meinhard von</t>
+  </si>
+  <si>
+    <t>Musikalischer Leiter</t>
+  </si>
+  <si>
+    <t>Ludwig, Heinz</t>
+  </si>
+  <si>
+    <t>Anouilh, Jean</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Friedl, Edith</t>
+  </si>
+  <si>
+    <t>Schauspieler:in</t>
+  </si>
+  <si>
+    <t>Ecker, Norbert</t>
+  </si>
+  <si>
+    <t>Stari, Willi</t>
+  </si>
+  <si>
+    <t>Sutermeister, Heinrich</t>
   </si>
 </sst>
 </file>
@@ -2280,7 +2838,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2301,20 +2859,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFDED"/>
+        <bgColor rgb="FFFFFDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDED"/>
-        <bgColor rgb="FFFFFDED"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -2352,7 +2916,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="50">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2366,13 +2930,13 @@
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2381,78 +2945,122 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2683,51 +3291,47 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2735,10 +3339,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -2746,3663 +3350,4785 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="E8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>23</v>
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="8" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>85</v>
+        <v>78</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="A34" s="3"/>
       <c r="B34" s="16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A35" s="3"/>
       <c r="B35" s="9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>91</v>
+        <v>83</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>96</v>
+      <c r="A38" s="3"/>
+      <c r="B38" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>99</v>
+        <v>71</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>102</v>
+      <c r="A40" s="3"/>
+      <c r="B40" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>105</v>
+        <v>92</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="20" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>111</v>
+        <v>97</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20" t="s">
-        <v>114</v>
+        <v>100</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>116</v>
+        <v>102</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>118</v>
+        <v>104</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>120</v>
+        <v>106</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>122</v>
+        <v>109</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>124</v>
+        <v>111</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="A51" s="3"/>
       <c r="B51" s="9" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>132</v>
+      <c r="A52" s="3"/>
+      <c r="B52" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="A53" s="3"/>
       <c r="B53" s="9" t="s">
-        <v>134</v>
+        <v>121</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>111</v>
+        <v>125</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>7</v>
+        <v>128</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>146</v>
+        <v>134</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>135</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>147</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>149</v>
+        <v>136</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>153</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>155</v>
+        <v>140</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>161</v>
+        <v>144</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>163</v>
+      <c r="A64" s="3"/>
+      <c r="B64" s="18" t="s">
+        <v>145</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="A65" s="3"/>
       <c r="B65" s="9" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>167</v>
+      <c r="A66" s="3"/>
+      <c r="B66" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>7</v>
+      <c r="A67" s="3"/>
+      <c r="B67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>7</v>
+        <v>153</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>173</v>
+      <c r="A69" s="3"/>
+      <c r="B69" s="13" t="s">
+        <v>155</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>7</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>7</v>
+        <v>162</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B74" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>111</v>
+      <c r="A74" s="3"/>
+      <c r="B74" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>186</v>
+      <c r="A75" s="3"/>
+      <c r="B75" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>189</v>
+      <c r="A76" s="3"/>
+      <c r="B76" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B77" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="A78" s="3"/>
       <c r="B78" s="9" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>193</v>
+      <c r="A79" s="3"/>
+      <c r="B79" s="18" t="s">
+        <v>168</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>26</v>
+        <v>169</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>199</v>
+        <v>171</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>172</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>199</v>
+      <c r="A82" s="3"/>
+      <c r="B82" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="A84" s="3"/>
       <c r="B84" s="9" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>208</v>
+        <v>178</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>210</v>
+      <c r="A86" s="3"/>
+      <c r="B86" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>215</v>
+        <v>188</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="2" t="s">
-        <v>217</v>
-      </c>
+      <c r="A90" s="3"/>
       <c r="B90" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="C91" s="19"/>
-      <c r="D91" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="E91" s="20" t="s">
-        <v>223</v>
+        <v>192</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>225</v>
+        <v>194</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>55</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
+        <v>198</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A95" s="3"/>
       <c r="B95" s="9" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>232</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>235</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>111</v>
+        <v>205</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>240</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B99" s="24" t="s">
-        <v>242</v>
+        <v>209</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>210</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>243</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B102" s="15" t="s">
-        <v>250</v>
+        <v>216</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>252</v>
+        <v>218</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>219</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>253</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E105" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" s="18" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>259</v>
+        <v>224</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>261</v>
+      <c r="A107" s="3"/>
+      <c r="B107" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B108" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="E108" s="9" t="s">
-        <v>97</v>
+        <v>227</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>265</v>
+        <v>230</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>231</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>42</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>275</v>
+        <v>240</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B114" s="25" t="s">
-        <v>277</v>
+        <v>242</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B115" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="E115" s="17" t="s">
-        <v>280</v>
+        <v>244</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>282</v>
+        <v>247</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>245</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>280</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>92</v>
+        <v>248</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>7</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>286</v>
+        <v>251</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>252</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>42</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B120" s="13" t="s">
-        <v>291</v>
+        <v>256</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>293</v>
+      <c r="A121" s="3"/>
+      <c r="B121" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>63</v>
+        <v>259</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B122" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="E122" s="9" t="s">
-        <v>82</v>
+        <v>260</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>297</v>
+      <c r="A123" s="3"/>
+      <c r="B123" s="16" t="s">
+        <v>261</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>301</v>
+        <v>267</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>268</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>303</v>
+        <v>77</v>
+      </c>
+      <c r="B126" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B127" s="13" t="s">
-        <v>305</v>
+        <v>269</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B128" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>7</v>
+        <v>272</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C128" s="10"/>
+      <c r="D128" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>308</v>
+        <v>276</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>277</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B130" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C130" s="19"/>
-      <c r="D130" s="19"/>
-      <c r="E130" s="20" t="s">
-        <v>311</v>
+      <c r="A130" s="3"/>
+      <c r="B130" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="E131" s="9" t="s">
-        <v>232</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B132" s="27" t="s">
-        <v>315</v>
+        <v>281</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>282</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B133" s="9" t="s">
-        <v>316</v>
+      <c r="A133" s="3"/>
+      <c r="B133" s="18" t="s">
+        <v>282</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>319</v>
+      <c r="A134" s="3"/>
+      <c r="B134" s="21" t="s">
+        <v>282</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>321</v>
+        <v>284</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>147</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>326</v>
+      <c r="A137" s="3"/>
+      <c r="B137" s="12" t="s">
+        <v>289</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B138" s="27" t="s">
-        <v>328</v>
+        <v>291</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>143</v>
+        <v>294</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E139" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B140" s="14" t="s">
-        <v>332</v>
+        <v>296</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B141" s="9" t="s">
-        <v>335</v>
+        <v>299</v>
+      </c>
+      <c r="B141" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>337</v>
+      <c r="A142" s="3"/>
+      <c r="B142" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="2" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B144" s="25" t="s">
-        <v>342</v>
+        <v>307</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>308</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B145" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="C145" s="9" t="s">
-        <v>345</v>
+        <v>309</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>310</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B148" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="E148" s="9" t="s">
-        <v>63</v>
+      <c r="A148" s="3"/>
+      <c r="B148" s="9" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B149" s="25" t="s">
-        <v>353</v>
+        <v>317</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B150" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="E150" s="17" t="s">
-        <v>111</v>
+        <v>319</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B151" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="E151" s="17" t="s">
-        <v>358</v>
+        <v>321</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B152" s="9" t="s">
-        <v>360</v>
+        <v>323</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>324</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>361</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B153" s="28" t="s">
-        <v>363</v>
+        <v>325</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>326</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="D154" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="E154" s="19" t="s">
-        <v>368</v>
+        <v>328</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B155" s="17" t="s">
-        <v>370</v>
+      <c r="A155" s="3"/>
+      <c r="B155" s="21" t="s">
+        <v>329</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>371</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="2" t="s">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="2" t="s">
-        <v>374</v>
+        <v>332</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>375</v>
+        <v>333</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>334</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>376</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B158" s="17" t="s">
-        <v>378</v>
+      <c r="A158" s="3"/>
+      <c r="B158" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B160" s="17" t="s">
-        <v>382</v>
+        <v>339</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>63</v>
+        <v>341</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>384</v>
+        <v>342</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>343</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B162" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>82</v>
+        <v>344</v>
+      </c>
+      <c r="B162" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="E162" s="18" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B163" s="24" t="s">
-        <v>388</v>
+        <v>347</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>348</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B164" s="9" t="s">
-        <v>391</v>
+      <c r="A164" s="3"/>
+      <c r="B164" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>82</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B165" s="14" t="s">
-        <v>393</v>
+        <v>351</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>352</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>82</v>
+        <v>353</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B166" s="15" t="s">
-        <v>395</v>
+      <c r="A166" s="3"/>
+      <c r="B166" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>7</v>
+        <v>355</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="E167" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>399</v>
+        <v>358</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>359</v>
       </c>
       <c r="E168" s="9" t="s">
-        <v>253</v>
+        <v>48</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>401</v>
+        <v>361</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>362</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>402</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B170" s="9" t="s">
-        <v>404</v>
+        <v>363</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>406</v>
+        <v>242</v>
+      </c>
+      <c r="B171" s="18" t="s">
+        <v>365</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B172" s="9" t="s">
-        <v>408</v>
+        <v>366</v>
+      </c>
+      <c r="B172" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>409</v>
+        <v>368</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="2" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="2" t="s">
-        <v>412</v>
+        <v>218</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>26</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B176" s="23" t="s">
-        <v>415</v>
-      </c>
-      <c r="E176" s="17" t="s">
-        <v>280</v>
+        <v>374</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="2" t="s">
-        <v>416</v>
-      </c>
+      <c r="A177" s="3"/>
       <c r="B177" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>26</v>
+        <v>355</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B178" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E178" s="9" t="s">
-        <v>7</v>
+        <v>377</v>
+      </c>
+      <c r="B178" s="14" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="B179" s="13" t="s">
-        <v>420</v>
+      <c r="A179" s="3"/>
+      <c r="B179" s="16" t="s">
+        <v>379</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>63</v>
+        <v>380</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B180" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>424</v>
+        <v>381</v>
+      </c>
+      <c r="B180" s="14" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>426</v>
+        <v>71</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>383</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>428</v>
+      <c r="A182" s="3"/>
+      <c r="B182" s="18" t="s">
+        <v>384</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>143</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>430</v>
+      <c r="A183" s="3"/>
+      <c r="B183" s="21" t="s">
+        <v>384</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="E184" s="9" t="s">
-        <v>26</v>
+        <v>385</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="C184" s="10"/>
+      <c r="D184" s="10"/>
+      <c r="E184" s="11" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>433</v>
+        <v>388</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>26</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B186" s="9" t="s">
-        <v>436</v>
+        <v>390</v>
+      </c>
+      <c r="B186" s="29" t="s">
+        <v>391</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>437</v>
+        <v>242</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>7</v>
+        <v>393</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B188" s="28" t="s">
-        <v>440</v>
+        <v>394</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B189" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="E189" s="17" t="s">
-        <v>111</v>
+        <v>396</v>
+      </c>
+      <c r="B189" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B190" s="14" t="s">
-        <v>444</v>
+        <v>398</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>400</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>445</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="2" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B192" s="13" t="s">
-        <v>449</v>
+        <v>403</v>
+      </c>
+      <c r="B192" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B193" s="14" t="s">
-        <v>451</v>
+        <v>405</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>406</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="2" t="s">
-        <v>452</v>
-      </c>
+      <c r="A194" s="3"/>
       <c r="B194" s="9" t="s">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>455</v>
+        <v>408</v>
+      </c>
+      <c r="B195" s="15" t="s">
+        <v>409</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="E196" s="9" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="D197" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E197" s="9" t="s">
-        <v>63</v>
+        <v>413</v>
+      </c>
+      <c r="B197" s="18" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="2" t="s">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>464</v>
+        <v>415</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>42</v>
+        <v>416</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="3"/>
+      <c r="A199" s="2" t="s">
+        <v>417</v>
+      </c>
       <c r="B199" s="9" t="s">
-        <v>465</v>
+        <v>418</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>419</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>467</v>
+      <c r="A200" s="3"/>
+      <c r="B200" s="12" t="s">
+        <v>418</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B201" s="15" t="s">
-        <v>469</v>
+      <c r="A201" s="3"/>
+      <c r="B201" s="21" t="s">
+        <v>418</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>7</v>
+        <v>167</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B202" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="D202" s="9" t="s">
-        <v>472</v>
+        <v>420</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>421</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>474</v>
+        <v>422</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>424</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>424</v>
+        <v>51</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="2" t="s">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>477</v>
+        <v>293</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="B205" s="13" t="s">
-        <v>479</v>
+      <c r="A205" s="3"/>
+      <c r="B205" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>481</v>
+        <v>428</v>
+      </c>
+      <c r="B206" s="19" t="s">
+        <v>429</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>483</v>
+        <v>430</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>431</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>484</v>
+        <v>70</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B208" s="24" t="s">
-        <v>486</v>
+      <c r="A208" s="3"/>
+      <c r="B208" s="30" t="s">
+        <v>432</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>487</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>489</v>
+        <v>433</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B210" s="14" t="s">
-        <v>491</v>
+      <c r="A210" s="3"/>
+      <c r="B210" s="12" t="s">
+        <v>435</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>493</v>
+      <c r="A211" s="3"/>
+      <c r="B211" s="12" t="s">
+        <v>436</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B212" s="13" t="s">
-        <v>495</v>
+        <v>437</v>
+      </c>
+      <c r="B212" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="E212" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B213" s="13" t="s">
-        <v>497</v>
+      <c r="A213" s="3"/>
+      <c r="B213" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B214" s="17" t="s">
-        <v>499</v>
+        <v>440</v>
+      </c>
+      <c r="B214" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="E214" s="18" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B215" s="21" t="s">
-        <v>501</v>
+        <v>443</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>358</v>
+        <v>445</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>503</v>
+        <v>446</v>
+      </c>
+      <c r="B216" s="31" t="s">
+        <v>447</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B217" s="29" t="s">
-        <v>505</v>
-      </c>
-      <c r="E217" s="17" t="s">
-        <v>506</v>
+        <v>448</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B218" s="25" t="s">
-        <v>508</v>
+      <c r="A218" s="3"/>
+      <c r="B218" s="21" t="s">
+        <v>449</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>510</v>
+        <v>453</v>
+      </c>
+      <c r="B219" s="18" t="s">
+        <v>454</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>7</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="2" t="s">
-        <v>511</v>
-      </c>
+      <c r="A220" s="3"/>
       <c r="B220" s="9" t="s">
-        <v>512</v>
+        <v>456</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>513</v>
+        <v>457</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="2" t="s">
-        <v>514</v>
+        <v>458</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>63</v>
+        <v>293</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="2" t="s">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>517</v>
+        <v>461</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="E223" s="9" t="s">
-        <v>45</v>
+        <v>463</v>
+      </c>
+      <c r="B223" s="18" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="2" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>521</v>
+        <v>466</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>522</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B225" s="17" t="s">
-        <v>524</v>
+        <v>467</v>
+      </c>
+      <c r="B225" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="2" t="s">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>527</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>529</v>
+        <v>471</v>
+      </c>
+      <c r="B227" s="15" t="s">
+        <v>472</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>531</v>
+        <v>473</v>
+      </c>
+      <c r="B228" s="25" t="s">
+        <v>474</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>235</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="2" t="s">
-        <v>532</v>
+        <v>104</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>533</v>
+        <v>476</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="2" t="s">
-        <v>534</v>
+        <v>477</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>535</v>
+        <v>478</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="B231" s="24" t="s">
-        <v>537</v>
+      <c r="A231" s="3"/>
+      <c r="B231" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>538</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>540</v>
+        <v>481</v>
+      </c>
+      <c r="B232" s="15" t="s">
+        <v>482</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>541</v>
+        <v>483</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>484</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="E234" s="9" t="s">
-        <v>544</v>
+        <v>485</v>
+      </c>
+      <c r="B234" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="E234" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="2" t="s">
-        <v>545</v>
+        <v>487</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>546</v>
+        <v>488</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>55</v>
+        <v>313</v>
       </c>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="B236" s="17" t="s">
-        <v>548</v>
+        <v>489</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>490</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>358</v>
+        <v>491</v>
       </c>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="2" t="s">
-        <v>549</v>
+        <v>492</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>550</v>
+        <v>493</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>551</v>
+        <v>48</v>
       </c>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B238" s="24" t="s">
-        <v>553</v>
+      <c r="A238" s="3"/>
+      <c r="B238" s="9" t="s">
+        <v>494</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>554</v>
+        <v>51</v>
       </c>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="2" t="s">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>557</v>
+        <v>70</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="B240" s="23" t="s">
-        <v>559</v>
+        <v>497</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="B241" s="25" t="s">
-        <v>561</v>
+        <v>339</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>498</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="B242" s="30" t="s">
-        <v>563</v>
+        <v>499</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>500</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>564</v>
+        <v>293</v>
       </c>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B243" s="13" t="s">
-        <v>566</v>
+        <v>501</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>502</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>567</v>
+        <v>29</v>
       </c>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="B244" s="23" t="s">
-        <v>569</v>
+      <c r="A244" s="3"/>
+      <c r="B244" s="9" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="E245" s="9" t="s">
-        <v>63</v>
+        <v>504</v>
+      </c>
+      <c r="B245" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="E245" s="18" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="2" t="s">
-        <v>572</v>
+        <v>506</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>573</v>
+        <v>507</v>
+      </c>
+      <c r="D246" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="B247" s="20" t="s">
-        <v>575</v>
+        <v>509</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>510</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>577</v>
+      <c r="A248" s="3"/>
+      <c r="B248" s="21" t="s">
+        <v>510</v>
       </c>
       <c r="E248" s="9" t="s">
-        <v>213</v>
+        <v>283</v>
       </c>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="2" t="s">
-        <v>179</v>
+        <v>511</v>
       </c>
       <c r="B249" s="9" t="s">
-        <v>578</v>
+        <v>512</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>63</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B250" s="31" t="s">
-        <v>580</v>
+        <v>514</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>515</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B251" s="13" t="s">
-        <v>582</v>
+        <v>516</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="2" t="s">
-        <v>583</v>
+        <v>518</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>584</v>
+        <v>519</v>
       </c>
       <c r="E252" s="9" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="2" t="s">
-        <v>585</v>
+        <v>520</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="D253" s="9" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="E253" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="B254" s="14" t="s">
-        <v>589</v>
+        <v>522</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>523</v>
       </c>
       <c r="E254" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="B255" s="32" t="s">
-        <v>591</v>
+        <v>524</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>525</v>
       </c>
       <c r="E255" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>593</v>
+      <c r="A256" s="3"/>
+      <c r="B256" s="13" t="s">
+        <v>525</v>
       </c>
       <c r="E256" s="9" t="s">
-        <v>594</v>
+        <v>526</v>
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="B257" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="C257" s="19"/>
-      <c r="D257" s="19"/>
-      <c r="E257" s="20"/>
+        <v>527</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>598</v>
+        <v>529</v>
+      </c>
+      <c r="B258" s="31" t="s">
+        <v>530</v>
       </c>
       <c r="E258" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="B259" s="20" t="s">
-        <v>600</v>
+        <v>531</v>
+      </c>
+      <c r="B259" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="E259" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B260" s="20" t="s">
-        <v>602</v>
-      </c>
-      <c r="C260" s="19"/>
-      <c r="D260" s="19"/>
-      <c r="E260" s="20" t="s">
-        <v>603</v>
+        <v>533</v>
+      </c>
+      <c r="B260" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E260" s="9" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B261" s="13" t="s">
-        <v>605</v>
+        <v>247</v>
+      </c>
+      <c r="B261" s="26" t="s">
+        <v>536</v>
       </c>
       <c r="E261" s="9" t="s">
-        <v>606</v>
+        <v>29</v>
       </c>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B262" s="13" t="s">
-        <v>608</v>
+        <v>537</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>538</v>
       </c>
       <c r="E262" s="9" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B263" s="17" t="s">
-        <v>610</v>
+      <c r="A263" s="3"/>
+      <c r="B263" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>612</v>
+      <c r="A264" s="3"/>
+      <c r="B264" s="21" t="s">
+        <v>541</v>
       </c>
       <c r="E264" s="9" t="s">
-        <v>7</v>
+        <v>542</v>
       </c>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="B265" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="E265" s="9" t="s">
-        <v>26</v>
+        <v>543</v>
+      </c>
+      <c r="B265" s="14" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="B266" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="E266" s="17" t="s">
-        <v>111</v>
+        <v>545</v>
+      </c>
+      <c r="B266" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="B267" s="14" t="s">
-        <v>618</v>
+        <v>547</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="E267" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="2" t="s">
-        <v>619</v>
-      </c>
+      <c r="A268" s="3"/>
       <c r="B268" s="9" t="s">
-        <v>620</v>
+        <v>549</v>
       </c>
       <c r="E268" s="9" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B269" s="25" t="s">
-        <v>622</v>
+        <v>550</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>551</v>
       </c>
       <c r="E269" s="9" t="s">
-        <v>623</v>
+        <v>552</v>
       </c>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="B270" s="30" t="s">
-        <v>625</v>
+        <v>553</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="E270" s="9" t="s">
-        <v>626</v>
+        <v>555</v>
       </c>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>628</v>
+      <c r="A271" s="3"/>
+      <c r="B271" s="18" t="s">
+        <v>554</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>85</v>
+        <v>556</v>
       </c>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="B272" s="15" t="s">
-        <v>630</v>
+        <v>557</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>559</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>632</v>
+      <c r="A273" s="3"/>
+      <c r="B273" s="12" t="s">
+        <v>558</v>
       </c>
       <c r="E273" s="9" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>634</v>
+      <c r="A274" s="3"/>
+      <c r="B274" s="21" t="s">
+        <v>558</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>26</v>
+        <v>283</v>
       </c>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="B275" s="23" t="s">
-        <v>636</v>
+        <v>560</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="E275" s="9" t="s">
-        <v>637</v>
+        <v>48</v>
       </c>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="2" t="s">
-        <v>638</v>
-      </c>
+      <c r="A276" s="3"/>
       <c r="B276" s="9" t="s">
-        <v>639</v>
+        <v>562</v>
       </c>
       <c r="E276" s="9" t="s">
-        <v>235</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="2" t="s">
-        <v>640</v>
+        <v>563</v>
       </c>
       <c r="B277" s="9" t="s">
-        <v>641</v>
+        <v>564</v>
       </c>
       <c r="E277" s="9" t="s">
-        <v>7</v>
+        <v>288</v>
       </c>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="B278" s="13" t="s">
-        <v>643</v>
+        <v>565</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E278" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="B279" s="14" t="s">
-        <v>645</v>
+        <v>567</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D279" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="E279" s="9" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B280" s="17" t="s">
-        <v>647</v>
-      </c>
-      <c r="E280" s="17" t="s">
-        <v>111</v>
+        <v>570</v>
+      </c>
+      <c r="B280" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="E280" s="9" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="2" t="s">
-        <v>648</v>
+        <v>572</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>649</v>
+        <v>573</v>
       </c>
       <c r="E281" s="9" t="s">
-        <v>26</v>
+        <v>574</v>
       </c>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="2" t="s">
-        <v>650</v>
-      </c>
+      <c r="A282" s="3"/>
       <c r="B282" s="9" t="s">
-        <v>651</v>
+        <v>575</v>
       </c>
       <c r="E282" s="9" t="s">
-        <v>652</v>
+        <v>576</v>
       </c>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B283" s="33" t="s">
-        <v>654</v>
-      </c>
+      <c r="A283" s="3"/>
+      <c r="B283" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="C283" s="33"/>
       <c r="E283" s="9" t="s">
-        <v>19</v>
+        <v>578</v>
       </c>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="B284" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="C284" s="34" t="s">
-        <v>657</v>
-      </c>
-      <c r="D284" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="E284" s="20" t="s">
-        <v>658</v>
+        <v>579</v>
+      </c>
+      <c r="B284" s="14" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="2" t="s">
-        <v>659</v>
+        <v>581</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>660</v>
+        <v>582</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>661</v>
+        <v>29</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="B286" s="23" t="s">
-        <v>663</v>
-      </c>
-      <c r="E286" s="17" t="s">
-        <v>280</v>
+        <v>583</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="E286" s="9" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="2" t="s">
-        <v>664</v>
-      </c>
+      <c r="A287" s="3"/>
       <c r="B287" s="9" t="s">
-        <v>665</v>
+        <v>586</v>
       </c>
       <c r="E287" s="9" t="s">
-        <v>666</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B288" s="9" t="s">
-        <v>668</v>
+        <v>587</v>
+      </c>
+      <c r="B288" s="25" t="s">
+        <v>588</v>
       </c>
       <c r="E288" s="9" t="s">
-        <v>7</v>
+        <v>589</v>
       </c>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="B289" s="17" t="s">
-        <v>670</v>
+      <c r="A289" s="3"/>
+      <c r="B289" s="18" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="B290" s="24" t="s">
-        <v>672</v>
+        <v>591</v>
+      </c>
+      <c r="B290" s="9" t="s">
+        <v>592</v>
       </c>
       <c r="E290" s="9" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B291" s="9" t="s">
-        <v>674</v>
+        <v>593</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>594</v>
       </c>
       <c r="E291" s="9" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="2" t="s">
-        <v>675</v>
+        <v>595</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>676</v>
+        <v>596</v>
       </c>
       <c r="E292" s="9" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="B293" s="9" t="s">
-        <v>678</v>
+      <c r="A293" s="3"/>
+      <c r="B293" s="16" t="s">
+        <v>597</v>
       </c>
       <c r="E293" s="9" t="s">
-        <v>679</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="B294" s="17" t="s">
-        <v>681</v>
+        <v>598</v>
+      </c>
+      <c r="B294" s="14" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="B295" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="E295" s="9" t="s">
-        <v>7</v>
+        <v>600</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B296" s="17" t="s">
-        <v>685</v>
+      <c r="A296" s="3"/>
+      <c r="B296" s="9" t="s">
+        <v>602</v>
       </c>
       <c r="E296" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B297" s="27" t="s">
-        <v>687</v>
-      </c>
-      <c r="E297" s="9" t="s">
-        <v>7</v>
+        <v>603</v>
+      </c>
+      <c r="B297" s="18" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B298" s="13" t="s">
-        <v>689</v>
+        <v>605</v>
+      </c>
+      <c r="B298" s="9" t="s">
+        <v>606</v>
       </c>
       <c r="E298" s="9" t="s">
-        <v>63</v>
+        <v>607</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="B299" s="14" t="s">
-        <v>691</v>
+      <c r="A299" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="B299" s="9" t="s">
+        <v>609</v>
       </c>
       <c r="E299" s="9" t="s">
-        <v>7</v>
+        <v>442</v>
       </c>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="B300" s="13" t="s">
-        <v>693</v>
+      <c r="A300" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="B300" s="9" t="s">
+        <v>611</v>
       </c>
       <c r="E300" s="9" t="s">
-        <v>484</v>
+        <v>70</v>
       </c>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B301" s="25" t="s">
-        <v>695</v>
-      </c>
-      <c r="E301" s="9" t="s">
-        <v>7</v>
+      <c r="A301" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B301" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="E301" s="18" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="2" t="s">
-        <v>696</v>
+      <c r="A302" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="B302" s="9" t="s">
-        <v>697</v>
+        <v>615</v>
       </c>
       <c r="E302" s="9" t="s">
-        <v>26</v>
+        <v>616</v>
       </c>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B303" s="9" t="s">
-        <v>699</v>
+      <c r="A303" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>618</v>
       </c>
       <c r="E303" s="9" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B304" s="9" t="s">
-        <v>701</v>
+      <c r="A304" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="B304" s="19" t="s">
+        <v>620</v>
       </c>
       <c r="E304" s="9" t="s">
-        <v>702</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B305" s="16" t="s">
-        <v>703</v>
+      <c r="A305" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>622</v>
       </c>
       <c r="E305" s="9" t="s">
-        <v>63</v>
+        <v>623</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="2" t="s">
-        <v>195</v>
+      <c r="A306" s="9" t="s">
+        <v>624</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>704</v>
+        <v>625</v>
       </c>
       <c r="E306" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B307" s="17" t="s">
-        <v>705</v>
-      </c>
-      <c r="E307" s="9" t="s">
-        <v>7</v>
+      <c r="A307" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="B307" s="9" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="9" t="s">
-        <v>92</v>
+        <v>628</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>706</v>
+        <v>70</v>
       </c>
       <c r="E308" s="9" t="s">
-        <v>707</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B309" s="9" t="s">
-        <v>708</v>
+      <c r="B309" s="13" t="s">
+        <v>629</v>
       </c>
       <c r="E309" s="9" t="s">
-        <v>709</v>
+        <v>630</v>
       </c>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="9" t="s">
-        <v>179</v>
+        <v>631</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>710</v>
+        <v>632</v>
       </c>
       <c r="E310" s="9" t="s">
-        <v>711</v>
+        <v>51</v>
       </c>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="9" t="s">
-        <v>409</v>
+        <v>633</v>
       </c>
       <c r="B311" s="9" t="s">
-        <v>712</v>
+        <v>634</v>
       </c>
       <c r="E311" s="9" t="s">
-        <v>713</v>
+        <v>635</v>
       </c>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>714</v>
+      <c r="B312" s="12" t="s">
+        <v>636</v>
       </c>
       <c r="E312" s="9" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B313" s="35" t="s">
-        <v>715</v>
-      </c>
-      <c r="E313" s="9" t="s">
-        <v>26</v>
+        <v>637</v>
+      </c>
+      <c r="B313" s="18" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="9" t="s">
-        <v>90</v>
+        <v>639</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>716</v>
+        <v>640</v>
       </c>
       <c r="E314" s="9" t="s">
-        <v>26</v>
+        <v>641</v>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B315" s="35" t="s">
-        <v>717</v>
+        <v>642</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>643</v>
       </c>
       <c r="E315" s="9" t="s">
-        <v>26</v>
+        <v>265</v>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="9" t="s">
-        <v>718</v>
+        <v>644</v>
       </c>
       <c r="B316" s="9" t="s">
-        <v>719</v>
+        <v>645</v>
       </c>
       <c r="E316" s="9" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="B317" s="9" t="s">
-        <v>721</v>
+      <c r="B317" s="12" t="s">
+        <v>646</v>
       </c>
       <c r="E317" s="9" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="9" t="s">
-        <v>722</v>
+        <v>647</v>
       </c>
       <c r="B318" s="9" t="s">
-        <v>723</v>
+        <v>648</v>
       </c>
       <c r="E318" s="9" t="s">
-        <v>724</v>
+        <v>61</v>
       </c>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="9" t="s">
-        <v>725</v>
+        <v>649</v>
       </c>
       <c r="B319" s="9" t="s">
-        <v>726</v>
+        <v>650</v>
       </c>
       <c r="E319" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="B320" s="9" t="s">
-        <v>728</v>
+      <c r="B320" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="E320" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="B321" s="9" t="s">
-        <v>730</v>
+        <v>652</v>
+      </c>
+      <c r="B321" s="25" t="s">
+        <v>653</v>
       </c>
       <c r="E321" s="9" t="s">
-        <v>731</v>
+        <v>654</v>
       </c>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="9" t="s">
-        <v>732</v>
+        <v>655</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>733</v>
+        <v>656</v>
+      </c>
+      <c r="E322" s="9" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="9" t="s">
-        <v>734</v>
+        <v>658</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="E323" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="9" t="s">
-        <v>735</v>
+      <c r="B324" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E324" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="9" t="s">
-        <v>736</v>
+        <v>104</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="E325" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="9" t="s">
-        <v>737</v>
+      <c r="B326" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="E326" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="9" t="s">
-        <v>738</v>
+        <v>663</v>
+      </c>
+      <c r="B327" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="E327" s="9" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="9" t="s">
-        <v>739</v>
+        <v>666</v>
+      </c>
+      <c r="B328" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="E328" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B329" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="E329" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="A330" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E330" s="9" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="A331" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B331" s="25" t="s">
+        <v>674</v>
+      </c>
+      <c r="E331" s="9" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="A332" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B332" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="E332" s="9" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="B333" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="E333" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="B334" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="E334" s="9" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="B335" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="E335" s="9" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="B336" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="E336" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="B337" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="E337" s="9" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="A338" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B338" s="23" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="A339" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B339" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="E339" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="A340" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B340" s="34" t="s">
+        <v>691</v>
+      </c>
+      <c r="E340" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="B341" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="E341" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="A342" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B342" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="E342" s="9" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="B343" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="E343" s="9" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="A344" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="B344" s="23" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="A345" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B345" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="E345" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="A346" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="B346" s="9" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="B347" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="E347" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="A348" s="9"/>
+      <c r="B348" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="E348" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="A349" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="B349" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="E349" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="A350" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="B350" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="E350" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="A351" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B351" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="E351" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="A352" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B352" s="35" t="s">
+        <v>713</v>
+      </c>
+      <c r="E352" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="B353" s="9" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="B354" s="16" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="A355" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="B355" s="14" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="A356" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="B356" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="E356" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="A357" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="B357" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="D357" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="E357" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="B358" s="18" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="B359" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="E359" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="A360" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B360" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="E360" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="A361" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="B361" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="E361" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="A362" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="B362" s="36" t="s">
+        <v>731</v>
+      </c>
+      <c r="E362" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="A363" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B363" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="E363" s="9" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="A364" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B364" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="C364" s="10"/>
+      <c r="D364" s="10"/>
+      <c r="E364" s="11"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="A365" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="B365" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="E365" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="A366" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B366" s="11" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="A367" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B367" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="C367" s="10"/>
+      <c r="D367" s="10"/>
+      <c r="E367" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="A368" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B368" s="9" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="A369" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="B369" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="E369" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="B370" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="E370" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="A371" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="B371" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="E371" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="B372" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="E372" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="A373" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="B373" s="18" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="A374" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="B374" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="E374" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="B375" s="13" t="s">
+        <v>755</v>
+      </c>
+      <c r="E375" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="B376" s="9" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="A377" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="E377" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="A378" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="B378" s="18" t="s">
+        <v>760</v>
+      </c>
+      <c r="E378" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="A379" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="B379" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="E379" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="B380" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="E380" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="A381" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="B381" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="E381" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="B382" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="E382" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="B383" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="E383" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="A384" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="B384" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E384" s="9" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="A385" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="B385" s="37" t="s">
+        <v>771</v>
+      </c>
+      <c r="E385" s="9" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="A386" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E386" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="B387" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E387" s="9" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="A388" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="B388" s="38" t="s">
+        <v>778</v>
+      </c>
+      <c r="E388" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="A389" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="E389" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="B390" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="A391" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="E391" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="A392" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="B392" s="39" t="s">
+        <v>784</v>
+      </c>
+      <c r="E392" s="9" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="A393" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E393" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="A394" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="B394" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="E394" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="A395" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="B395" s="14" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="B396" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="E396" s="9" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="B397" s="12" t="s">
+        <v>794</v>
+      </c>
+      <c r="E397" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="B398" s="40" t="s">
+        <v>794</v>
+      </c>
+      <c r="E398" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="A399" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="B399" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="E399" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="A400" s="9" t="s">
+        <v>797</v>
+      </c>
+      <c r="B400" s="18" t="s">
+        <v>798</v>
+      </c>
+      <c r="E400" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="B401" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="E401" s="9" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="B402" s="9" t="s">
+        <v>801</v>
+      </c>
+      <c r="E402" s="9" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="A403" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B403" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="E403" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="A404" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="B404" s="9" t="s">
+        <v>806</v>
+      </c>
+      <c r="E404" s="9" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="A405" s="9" t="s">
+        <v>808</v>
+      </c>
+      <c r="B405" s="41" t="s">
+        <v>809</v>
+      </c>
+      <c r="E405" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="B406" s="18" t="s">
+        <v>809</v>
+      </c>
+      <c r="E406" s="9" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="B407" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="E407" s="9" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="B408" s="9" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="A409" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="B409" s="11" t="s">
+        <v>814</v>
+      </c>
+      <c r="C409" s="42" t="s">
+        <v>815</v>
+      </c>
+      <c r="D409" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="E409" s="11" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="A410" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="B410" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="E410" s="9" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="A411" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="B411" s="23" t="s">
+        <v>821</v>
+      </c>
+      <c r="E411" s="18" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="A412" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="B412" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="E412" s="9" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="A413" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E413" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="A414" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="A415" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="B415" s="43" t="s">
+        <v>830</v>
+      </c>
+      <c r="E415" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="A416" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="E416" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="A417" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="B417" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="E417" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="A418" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E418" s="9" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="A419" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="B419" s="18" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="A420" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="B420" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="E420" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="A421" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="B421" s="18" t="s">
+        <v>843</v>
+      </c>
+      <c r="E421" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="B422" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="E422" s="9" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="A423" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="B423" s="44" t="s">
+        <v>847</v>
+      </c>
+      <c r="E423" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="A424" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="B424" s="14" t="s">
+        <v>849</v>
+      </c>
+      <c r="E424" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="A425" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="B425" s="15" t="s">
+        <v>851</v>
+      </c>
+      <c r="E425" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="A426" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B426" s="14" t="s">
+        <v>853</v>
+      </c>
+      <c r="E426" s="9" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="B427" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="E427" s="9" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="B428" s="18" t="s">
+        <v>856</v>
+      </c>
+      <c r="E428" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="B429" s="21" t="s">
+        <v>856</v>
+      </c>
+      <c r="E429" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="A430" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="E430" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="A431" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="B431" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="E431" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="A432" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="B432" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="E432" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="A433" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="B433" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="E433" s="45" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="A434" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="B434" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="E434" s="9" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="A435" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B435" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="E435" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="A436" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B436" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="E436" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="B437" s="21" t="s">
+        <v>870</v>
+      </c>
+      <c r="E437" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="A438" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E438" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="B439" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="E439" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="B440" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="E440" s="9" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="B441" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="E441" s="9" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="B442" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="E442" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="B443" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="E443" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="B444" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="E444" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="B445" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="E445" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="B446" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="E446" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="B447" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="E447" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="B448" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="E448" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="B449" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="E449" s="9" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="B450" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="E450" s="9" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="B451" s="9" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="B452" s="9" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="B453" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="E453" s="9" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="B454" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="E454" s="9" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="B455" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="E455" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="B456" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="E456" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="B457" s="46" t="s">
+        <v>895</v>
+      </c>
+      <c r="E457" s="9" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="B458" s="46" t="s">
+        <v>897</v>
+      </c>
+      <c r="E458" s="9" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="B459" s="47" t="s">
+        <v>899</v>
+      </c>
+      <c r="E459" s="9" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="B460" s="47" t="s">
+        <v>900</v>
+      </c>
+      <c r="E460" s="9" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="B461" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="E461" s="9" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="B462" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="E462" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="B463" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="E463" s="9" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="A464" s="48"/>
+      <c r="B464" s="33" t="s">
+        <v>907</v>
+      </c>
+      <c r="E464" s="9" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="B465" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="E465" s="9" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="B466" s="49" t="s">
+        <v>911</v>
+      </c>
+      <c r="E466" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="B467" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="E467" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="B468" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="E468" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="B469" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="E469" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="B470" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="E470" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="B471" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="E471" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="B472" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="E472" s="9" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="B473" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="E473" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="B474" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="E474" s="9" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="B475" s="12" t="s">
+        <v>922</v>
+      </c>
+      <c r="E475" s="9" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="B476" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="E476" s="9" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="B477" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="E477" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="B478" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="E478" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="479" ht="15.75" customHeight="1"/>
     <row r="480" ht="15.75" customHeight="1"/>
     <row r="481" ht="15.75" customHeight="1"/>
@@ -6862,26 +8588,6 @@
     <row r="935" ht="15.75" customHeight="1"/>
     <row r="936" ht="15.75" customHeight="1"/>
     <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
